--- a/static/bots/Aurula/interview.xlsx
+++ b/static/bots/Aurula/interview.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="23">
   <si>
     <t xml:space="preserve">description</t>
   </si>
@@ -74,19 +74,22 @@
     <t xml:space="preserve">location</t>
   </si>
   <si>
+    <t xml:space="preserve">user</t>
+  </si>
+  <si>
+    <t xml:space="preserve">他者</t>
+  </si>
+  <si>
+    <t xml:space="preserve">平静</t>
+  </si>
+  <si>
+    <t xml:space="preserve">向かい合う</t>
+  </si>
+  <si>
+    <t xml:space="preserve">私的</t>
+  </si>
+  <si>
     <t xml:space="preserve">bot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">誰か</t>
-  </si>
-  <si>
-    <t xml:space="preserve">平静</t>
-  </si>
-  <si>
-    <t xml:space="preserve">向かい合う</t>
-  </si>
-  <si>
-    <t xml:space="preserve">私的</t>
   </si>
 </sst>
 </file>
@@ -101,6 +104,7 @@
       <sz val="10"/>
       <name val="Noto Sans CJK JP"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -121,6 +125,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -165,16 +170,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -304,452 +313,452 @@
   <dimension ref="A1:H33"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="7.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="81.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="7.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="81.94"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>0.6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>0.4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <v>0.7</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="1" t="n">
         <v>0.2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="1" t="n">
         <v>0.2</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="1" t="n">
         <v>0.2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="1" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="1" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="0" t="n">
+      <c r="D12" s="1" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="0" t="n">
+      <c r="D13" s="1" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="H15" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G16" s="2" t="s">
+      <c r="B16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17" s="2" t="s">
+      <c r="A17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G18" s="2" t="s">
+      <c r="A18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G19" s="2" t="s">
+      <c r="A19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G20" s="2" t="s">
+      <c r="A20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G21" s="2" t="s">
+      <c r="A21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G22" s="2" t="s">
+      <c r="A22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G23" s="2" t="s">
+      <c r="A23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G24" s="2" t="s">
+      <c r="A24" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G25" s="2" t="s">
+      <c r="A25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G26" s="2" t="s">
+      <c r="A26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G27" s="2" t="s">
+      <c r="A27" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G28" s="2" t="s">
+      <c r="A28" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G28" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G29" s="2" t="s">
+      <c r="A29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G29" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G30" s="2" t="s">
+      <c r="A30" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G30" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G31" s="2" t="s">
+      <c r="A31" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G31" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G32" s="2" t="s">
+      <c r="A32" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G32" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G33" s="2" t="s">
+      <c r="A33" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G33" s="3" t="s">
         <v>21</v>
       </c>
     </row>
@@ -757,10 +766,6 @@
   <dataValidations count="5">
     <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A16:A33" type="list">
       <formula1>"bot,user"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B16:B33" type="list">
-      <formula1>"自身,誰か"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E16:E33" type="list">
@@ -773,6 +778,10 @@
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G16:G33" type="list">
       <formula1>"私的,公的"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B16:B33" type="list">
+      <formula1>"自身,他者"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
